--- a/examples/16_source_ref_showcase/products_config.xlsx
+++ b/examples/16_source_ref_showcase/products_config.xlsx
@@ -779,7 +779,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sqlite</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>products.db</t>
+          <t>excel_parser</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -809,6 +809,11 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>db_schema</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>showcase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">

--- a/examples/16_source_ref_showcase/products_config.xlsx
+++ b/examples/16_source_ref_showcase/products_config.xlsx
@@ -366,10 +366,14 @@
     expr:-{D}                  (negate a value)
     expr:{A} &amp; " - " &amp; {C}    (concatenate with separator)
     expr:{D} * 0.18            (calculate 18% tax)
+5. Positional map: 'map:v1||v2||v3||...' — assigns a different value to each row by position. The first data row gets v1, the second gets v2, and so on. Use || (double pipe) to separate values.
+  Example: map:Name||Area||City||ID||GSTIN
+  Ideal for key_value blocks where the source has no label column.
+  If the map has fewer values than rows, extra rows get NULL.
 All results are cast to the column's data_type. 'script' and
 'null_default' apply after the expression result is cast.
 IMPORTANT: if the supplier inserts a new column, every letter after it shifts. Re-check all col: and expr: source_ref values when that happens.
-Allowed: col:&lt;letter&gt;, const:&lt;value&gt;, fn:&lt;name&gt;, or expr:&lt;expression&gt;
+Allowed: col:&lt;letter&gt;, const:&lt;value&gt;, fn:&lt;name&gt;, expr:&lt;expression&gt;, or map:v1||v2||...
 Example: col:A</t>
       </text>
     </comment>
@@ -2504,6 +2508,10 @@
     expr:-{D}                  (negate a value)
     expr:{A} &amp; " - " &amp; {C}    (concatenate with separator)
     expr:{D} * 0.18            (calculate 18% tax)
+5. Positional map: 'map:v1||v2||v3||...' — assigns a different value to each row by position. The first data row gets v1, the second gets v2, and so on. Use || (double pipe) to separate values.
+  Example: map:Name||Area||City||ID||GSTIN
+  Ideal for key_value blocks where the source has no label column.
+  If the map has fewer values than rows, extra rows get NULL.
 All results are cast to the column's data_type. 'script' and
 'null_default' apply after the expression result is cast.
 IMPORTANT: if the supplier inserts a new column, every letter after it shifts. Re-check all col: and expr: source_ref values when that happens.</t>
@@ -2511,7 +2519,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>col:&lt;letter&gt;, const:&lt;value&gt;, fn:&lt;name&gt;, or expr:&lt;expression&gt;</t>
+          <t>col:&lt;letter&gt;, const:&lt;value&gt;, fn:&lt;name&gt;, expr:&lt;expression&gt;, or map:v1||v2||...</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
